--- a/human_resources_forms/048_human_resources_application_form--human_resources_forms.xlsx
+++ b/human_resources_forms/048_human_resources_application_form--human_resources_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -849,8 +849,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -878,12 +878,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'full-time',_'value':_'full-time'}</t>
+          <t>full-time</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Full-time', 'value': 'full-time'}</t>
+          <t>Full-time</t>
         </is>
       </c>
     </row>
@@ -895,12 +895,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'part-time',_'value':_'part-time'}</t>
+          <t>part-time</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Part-time', 'value': 'part-time'}</t>
+          <t>Part-time</t>
         </is>
       </c>
     </row>
@@ -912,12 +912,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'temporary',_'value':_'temporary'}</t>
+          <t>temporary</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Temporary', 'value': 'temporary'}</t>
+          <t>Temporary</t>
         </is>
       </c>
     </row>
@@ -929,12 +929,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'high_school',_'value':_'high_school'}</t>
+          <t>high_school</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'High School', 'value': 'high_school'}</t>
+          <t>High School</t>
         </is>
       </c>
     </row>
@@ -946,12 +946,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_"bachelor's_degree",_'value':_'bachelors_degree'}</t>
+          <t>bachelor's_degree</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': "Bachelor's Degree", 'value': 'bachelors_degree'}</t>
+          <t>Bachelor's Degree</t>
         </is>
       </c>
     </row>
@@ -963,12 +963,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_"master's_degree",_'value':_'masters_degree'}</t>
+          <t>master's_degree</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': "Master's Degree", 'value': 'masters_degree'}</t>
+          <t>Master's Degree</t>
         </is>
       </c>
     </row>
@@ -980,12 +980,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'ph.d.',_'value':_'phd'}</t>
+          <t>ph.d.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Ph.D.', 'value': 'phd'}</t>
+          <t>Ph.D.</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Other', 'value': 'other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1014,12 +1014,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'employed',_'value':_'employed'}</t>
+          <t>employed</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Employed', 'value': 'employed'}</t>
+          <t>Employed</t>
         </is>
       </c>
     </row>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'self-employed',_'value':_'self-employed'}</t>
+          <t>self-employed</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Self-Employed', 'value': 'self-employed'}</t>
+          <t>Self-Employed</t>
         </is>
       </c>
     </row>
@@ -1048,12 +1048,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'unemployed',_'value':_'unemployed'}</t>
+          <t>unemployed</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Unemployed', 'value': 'unemployed'}</t>
+          <t>Unemployed</t>
         </is>
       </c>
     </row>
@@ -1065,12 +1065,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Other', 'value': 'other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
